--- a/database/event/6510/event_6510_evp_summary.xlsx
+++ b/database/event/6510/event_6510_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9699</v>
+        <v>5.8047</v>
       </c>
       <c r="C2" t="n">
-        <v>2.519</v>
+        <v>2.4493</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9903</v>
+        <v>1.8687</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9699</v>
+        <v>5.8047</v>
       </c>
       <c r="F2" t="n">
-        <v>5.9699</v>
+        <v>5.8047</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.0577</v>
+        <v>6.7987</v>
       </c>
       <c r="I2" t="n">
         <v>7.3931</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6164</v>
+        <v>5.4642</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3699</v>
+        <v>2.3057</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8475</v>
+        <v>1.733</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6164</v>
+        <v>5.4642</v>
       </c>
       <c r="F3" t="n">
-        <v>5.6164</v>
+        <v>5.4642</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5034</v>
+        <v>6.2649</v>
       </c>
       <c r="I3" t="n">
         <v>6.8126</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9113</v>
+        <v>4.8349</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0724</v>
+        <v>2.0401</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5627</v>
+        <v>1.4823</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9113</v>
+        <v>4.8349</v>
       </c>
       <c r="F4" t="n">
-        <v>4.9113</v>
+        <v>4.8349</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3978</v>
+        <v>5.2781</v>
       </c>
       <c r="I4" t="n">
         <v>5.5503</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8358</v>
+        <v>4.7488</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0405</v>
+        <v>2.0038</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5322</v>
+        <v>1.448</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8358</v>
+        <v>4.7488</v>
       </c>
       <c r="F5" t="n">
-        <v>4.8358</v>
+        <v>4.7488</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2794</v>
+        <v>5.1431</v>
       </c>
       <c r="I5" t="n">
         <v>5.4538</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6933</v>
+        <v>4.575</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9804</v>
+        <v>1.9305</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4746</v>
+        <v>1.3788</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6933</v>
+        <v>4.575</v>
       </c>
       <c r="F6" t="n">
-        <v>4.6933</v>
+        <v>4.575</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.056</v>
+        <v>4.8706</v>
       </c>
       <c r="I6" t="n">
         <v>5.2964</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5947</v>
+        <v>4.5254</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9388</v>
+        <v>1.9095</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4348</v>
+        <v>1.359</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5947</v>
+        <v>4.5254</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5947</v>
+        <v>4.5254</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9015</v>
+        <v>4.7928</v>
       </c>
       <c r="I7" t="n">
         <v>5.0399</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8263</v>
+        <v>3.7695</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6145</v>
+        <v>1.5906</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1244</v>
+        <v>1.0579</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8263</v>
+        <v>3.7695</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8263</v>
+        <v>3.7695</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8263</v>
+        <v>3.7695</v>
       </c>
       <c r="I8" t="n">
         <v>3.898</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.695</v>
+        <v>3.5595</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5591</v>
+        <v>1.502</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0713</v>
+        <v>0.9742</v>
       </c>
       <c r="E9" t="n">
-        <v>3.695</v>
+        <v>3.5595</v>
       </c>
       <c r="F9" t="n">
-        <v>3.695</v>
+        <v>3.5595</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.695</v>
+        <v>3.5595</v>
       </c>
       <c r="I9" t="n">
         <v>3.8706</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2704</v>
+        <v>3.2098</v>
       </c>
       <c r="C10" t="n">
-        <v>1.38</v>
+        <v>1.3544</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8998</v>
+        <v>0.8349</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2704</v>
+        <v>3.2098</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2704</v>
+        <v>3.2098</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2704</v>
+        <v>3.2098</v>
       </c>
       <c r="I10" t="n">
         <v>3.3472</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1908</v>
+        <v>3.1317</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3464</v>
+        <v>1.3214</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8677</v>
+        <v>0.8038</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1908</v>
+        <v>3.1317</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1908</v>
+        <v>3.1317</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1908</v>
+        <v>3.1317</v>
       </c>
       <c r="I11" t="n">
         <v>3.2658</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.963</v>
+        <v>2.9081</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2503</v>
+        <v>1.2271</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7756</v>
+        <v>0.7147</v>
       </c>
       <c r="E12" t="n">
-        <v>2.963</v>
+        <v>2.9081</v>
       </c>
       <c r="F12" t="n">
-        <v>2.963</v>
+        <v>2.9081</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.963</v>
+        <v>2.9081</v>
       </c>
       <c r="I12" t="n">
         <v>3.0326</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6529</v>
+        <v>2.6233</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1194</v>
+        <v>1.1069</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6504</v>
+        <v>0.6012</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6529</v>
+        <v>2.6233</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6529</v>
+        <v>2.6233</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6529</v>
+        <v>2.6233</v>
       </c>
       <c r="I13" t="n">
         <v>2.6901</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5725</v>
+        <v>2.506</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0855</v>
+        <v>1.0574</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6179</v>
+        <v>0.5545</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5725</v>
+        <v>2.506</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5725</v>
+        <v>2.506</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5725</v>
+        <v>2.506</v>
       </c>
       <c r="I14" t="n">
         <v>2.6575</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.487</v>
+        <v>2.4409</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0494</v>
+        <v>1.03</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5833</v>
+        <v>0.5285</v>
       </c>
       <c r="E15" t="n">
-        <v>2.487</v>
+        <v>2.4409</v>
       </c>
       <c r="F15" t="n">
-        <v>2.487</v>
+        <v>2.4409</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.487</v>
+        <v>2.4409</v>
       </c>
       <c r="I15" t="n">
         <v>2.5454</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4704</v>
+        <v>2.4156</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0424</v>
+        <v>1.0193</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5766</v>
+        <v>0.5185</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4704</v>
+        <v>2.4156</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4704</v>
+        <v>2.4156</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4704</v>
+        <v>2.4156</v>
       </c>
       <c r="I16" t="n">
         <v>2.5402</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3666</v>
+        <v>2.3141</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9986</v>
+        <v>0.9765</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5347</v>
+        <v>0.478</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3666</v>
+        <v>2.3141</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3666</v>
+        <v>2.3141</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3666</v>
+        <v>2.3141</v>
       </c>
       <c r="I17" t="n">
         <v>2.4334</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0807</v>
+        <v>2.0575</v>
       </c>
       <c r="C18" t="n">
-        <v>0.878</v>
+        <v>0.8682</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4192</v>
+        <v>0.3758</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0807</v>
+        <v>2.0575</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0807</v>
+        <v>2.0575</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0807</v>
+        <v>2.0575</v>
       </c>
       <c r="I18" t="n">
         <v>2.1099</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0249</v>
+        <v>1.9949</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8544</v>
+        <v>0.8418</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3967</v>
+        <v>0.3509</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0249</v>
+        <v>1.9949</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0249</v>
+        <v>1.9949</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0249</v>
+        <v>1.9949</v>
       </c>
       <c r="I19" t="n">
         <v>2.0629</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9163</v>
+        <v>1.8878</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8086</v>
+        <v>0.7966</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3528</v>
+        <v>0.3082</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9163</v>
+        <v>1.8878</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9163</v>
+        <v>1.8878</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9163</v>
+        <v>1.8878</v>
       </c>
       <c r="I20" t="n">
         <v>1.9522</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7506</v>
+        <v>1.7246</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7387</v>
+        <v>0.7277</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2858</v>
+        <v>0.2432</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7506</v>
+        <v>1.7246</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7506</v>
+        <v>1.7246</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7506</v>
+        <v>1.7246</v>
       </c>
       <c r="I21" t="n">
         <v>1.7834</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.5311</v>
+        <v>1.5084</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6461</v>
+        <v>0.6365</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1972</v>
+        <v>0.157</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5311</v>
+        <v>1.5084</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5311</v>
+        <v>1.5084</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5311</v>
+        <v>1.5084</v>
       </c>
       <c r="I22" t="n">
         <v>1.5598</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.467</v>
+        <v>1.4615</v>
       </c>
       <c r="C23" t="n">
-        <v>0.619</v>
+        <v>0.6167</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1713</v>
+        <v>0.1384</v>
       </c>
       <c r="E23" t="n">
-        <v>1.467</v>
+        <v>1.4615</v>
       </c>
       <c r="F23" t="n">
-        <v>1.467</v>
+        <v>1.4615</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.467</v>
+        <v>1.4615</v>
       </c>
       <c r="I23" t="n">
         <v>1.4738</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.396</v>
+        <v>1.3753</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5891</v>
+        <v>0.5803</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1426</v>
+        <v>0.104</v>
       </c>
       <c r="E24" t="n">
-        <v>1.396</v>
+        <v>1.3753</v>
       </c>
       <c r="F24" t="n">
-        <v>1.396</v>
+        <v>1.3753</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.396</v>
+        <v>1.3753</v>
       </c>
       <c r="I24" t="n">
         <v>1.4222</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3858</v>
+        <v>1.3653</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5847</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1385</v>
+        <v>0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3858</v>
+        <v>1.3653</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3858</v>
+        <v>1.3653</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3858</v>
+        <v>1.3653</v>
       </c>
       <c r="I25" t="n">
         <v>1.4118</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3271</v>
+        <v>1.2784</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5394</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1148</v>
+        <v>0.0654</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3271</v>
+        <v>1.2784</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3271</v>
+        <v>1.2784</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3271</v>
+        <v>1.2784</v>
       </c>
       <c r="I26" t="n">
         <v>1.3902</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2734</v>
+        <v>1.2592</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5373</v>
+        <v>0.5313</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0931</v>
+        <v>0.0578</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2734</v>
+        <v>1.2592</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2734</v>
+        <v>1.2592</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2734</v>
+        <v>1.2592</v>
       </c>
       <c r="I27" t="n">
         <v>1.2913</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1377</v>
+        <v>1.1128</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4801</v>
+        <v>0.4696</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0382</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1377</v>
+        <v>1.1128</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1377</v>
+        <v>1.1128</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1377</v>
+        <v>1.1128</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1917</v>
+        <v>1.1222</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>399</v>
+        <v>150</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1917</v>
+        <v>1.1222</v>
       </c>
       <c r="N28" t="n">
-        <v>399</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.117</v>
+        <v>1.0959</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4713</v>
+        <v>0.4624</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0299</v>
+        <v>-0.0073</v>
       </c>
       <c r="E29" t="n">
-        <v>1.117</v>
+        <v>1.0959</v>
       </c>
       <c r="F29" t="n">
-        <v>1.117</v>
+        <v>1.0959</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.117</v>
+        <v>1.0959</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1222</v>
+        <v>1.1917</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>150</v>
+        <v>399</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1222</v>
+        <v>1.1917</v>
       </c>
       <c r="N29" t="n">
-        <v>150</v>
+        <v>399</v>
       </c>
     </row>
     <row r="30">
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0817</v>
+        <v>1.0776</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4564</v>
+        <v>0.4547</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0156</v>
+        <v>-0.0146</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0817</v>
+        <v>1.0776</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0817</v>
+        <v>1.0776</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0817</v>
+        <v>1.0776</v>
       </c>
       <c r="I30" t="n">
         <v>1.0867</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0289</v>
+        <v>1.0251</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4342</v>
+        <v>0.4325</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0057</v>
+        <v>-0.0355</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0289</v>
+        <v>1.0251</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0289</v>
+        <v>1.0251</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0289</v>
+        <v>1.0251</v>
       </c>
       <c r="I31" t="n">
         <v>1.0337</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.0059</v>
+        <v>0.991</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4244</v>
+        <v>0.4182</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.015</v>
+        <v>-0.0491</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0059</v>
+        <v>0.991</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0059</v>
+        <v>0.991</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0059</v>
+        <v>0.991</v>
       </c>
       <c r="I32" t="n">
         <v>1.0248</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9706</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4096</v>
+        <v>0.3945</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0293</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9706</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9706</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9706</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="I33" t="n">
         <v>1.0167</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.86</v>
+        <v>0.8409</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3629</v>
+        <v>0.3548</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.1089</v>
       </c>
       <c r="E34" t="n">
-        <v>0.86</v>
+        <v>0.8409</v>
       </c>
       <c r="F34" t="n">
-        <v>0.86</v>
+        <v>0.8409</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.86</v>
+        <v>0.8409</v>
       </c>
       <c r="I34" t="n">
         <v>0.8843</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7302</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3116</v>
+        <v>0.3081</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1231</v>
+        <v>-0.153</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7302</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7302</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7302</v>
       </c>
       <c r="I35" t="n">
         <v>0.7488</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7282</v>
+        <v>0.7201</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3073</v>
+        <v>0.3039</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1272</v>
+        <v>-0.157</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7282</v>
+        <v>0.7201</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7282</v>
+        <v>0.7201</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7282</v>
+        <v>0.7201</v>
       </c>
       <c r="I36" t="n">
         <v>0.7383999999999999</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6403</v>
+        <v>0.6379</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2702</v>
+        <v>0.2692</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1627</v>
+        <v>-0.1898</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6403</v>
+        <v>0.6379</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6403</v>
+        <v>0.6379</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6403</v>
+        <v>0.6379</v>
       </c>
       <c r="I37" t="n">
         <v>0.6433</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6169</v>
+        <v>0.6032</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2603</v>
+        <v>0.2545</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1721</v>
+        <v>-0.2036</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6169</v>
+        <v>0.6032</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6169</v>
+        <v>0.6032</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6169</v>
+        <v>0.6032</v>
       </c>
       <c r="I38" t="n">
         <v>0.6343</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.588</v>
+        <v>0.5793</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2481</v>
+        <v>0.2444</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1838</v>
+        <v>-0.2131</v>
       </c>
       <c r="E39" t="n">
-        <v>0.588</v>
+        <v>0.5793</v>
       </c>
       <c r="F39" t="n">
-        <v>0.588</v>
+        <v>0.5793</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.588</v>
+        <v>0.5793</v>
       </c>
       <c r="I39" t="n">
         <v>0.599</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5504</v>
+        <v>0.5443</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2322</v>
+        <v>0.2297</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.199</v>
+        <v>-0.2271</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5504</v>
+        <v>0.5443</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5504</v>
+        <v>0.5443</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5504</v>
+        <v>0.5443</v>
       </c>
       <c r="I40" t="n">
         <v>0.5582</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5138</v>
+        <v>0.5043</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2168</v>
+        <v>0.2128</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2138</v>
+        <v>-0.243</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5138</v>
+        <v>0.5043</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5138</v>
+        <v>0.5043</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5138</v>
+        <v>0.5043</v>
       </c>
       <c r="I41" t="n">
         <v>0.5259</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4742</v>
+        <v>0.4637</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2001</v>
+        <v>0.1957</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2298</v>
+        <v>-0.2592</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4742</v>
+        <v>0.4637</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4742</v>
+        <v>0.4637</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4742</v>
+        <v>0.4637</v>
       </c>
       <c r="I42" t="n">
         <v>0.4876</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.407</v>
+        <v>0.392</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1717</v>
+        <v>0.1654</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2569</v>
+        <v>-0.2877</v>
       </c>
       <c r="E43" t="n">
-        <v>0.407</v>
+        <v>0.392</v>
       </c>
       <c r="F43" t="n">
-        <v>0.407</v>
+        <v>0.392</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.407</v>
+        <v>0.392</v>
       </c>
       <c r="I43" t="n">
         <v>0.4263</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3404</v>
+        <v>0.3391</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1436</v>
+        <v>0.1431</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2838</v>
+        <v>-0.3088</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3404</v>
+        <v>0.3391</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3404</v>
+        <v>0.3391</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3404</v>
+        <v>0.3391</v>
       </c>
       <c r="I44" t="n">
         <v>0.342</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3151</v>
+        <v>0.3116</v>
       </c>
       <c r="C45" t="n">
-        <v>0.133</v>
+        <v>0.1315</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2941</v>
+        <v>-0.3198</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3151</v>
+        <v>0.3116</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3151</v>
+        <v>0.3116</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3151</v>
+        <v>0.3116</v>
       </c>
       <c r="I45" t="n">
         <v>0.3195</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2455</v>
+        <v>0.2419</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1036</v>
+        <v>0.1021</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3222</v>
+        <v>-0.3475</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2455</v>
+        <v>0.2419</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2455</v>
+        <v>0.2419</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2455</v>
+        <v>0.2419</v>
       </c>
       <c r="I46" t="n">
         <v>0.2501</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2445</v>
+        <v>0.2409</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1032</v>
+        <v>0.1016</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3226</v>
+        <v>-0.3479</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2445</v>
+        <v>0.2409</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2445</v>
+        <v>0.2409</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2445</v>
+        <v>0.2409</v>
       </c>
       <c r="I47" t="n">
         <v>0.2491</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.222</v>
+        <v>0.2211</v>
       </c>
       <c r="C48" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3317</v>
+        <v>-0.3558</v>
       </c>
       <c r="E48" t="n">
-        <v>0.222</v>
+        <v>0.2211</v>
       </c>
       <c r="F48" t="n">
-        <v>0.222</v>
+        <v>0.2211</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.222</v>
+        <v>0.2211</v>
       </c>
       <c r="I48" t="n">
         <v>0.223</v>
@@ -2664,7 +2664,7 @@
         <v>0.0757</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3488</v>
+        <v>-0.3724</v>
       </c>
       <c r="E49" t="n">
         <v>0.1795</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1003</v>
+        <v>0.0988</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0423</v>
+        <v>0.0417</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3808</v>
+        <v>-0.4045</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1003</v>
+        <v>0.0988</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1003</v>
+        <v>0.0988</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1003</v>
+        <v>0.0988</v>
       </c>
       <c r="I50" t="n">
         <v>0.1022</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0531</v>
+        <v>-0.0529</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0224</v>
+        <v>-0.0223</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4428</v>
+        <v>-0.465</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0531</v>
+        <v>-0.0529</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0531</v>
+        <v>-0.0529</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0531</v>
+        <v>-0.0529</v>
       </c>
       <c r="I51" t="n">
         <v>-0.0533</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1624</v>
+        <v>-0.1618</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0683</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.487</v>
+        <v>-0.5084</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1624</v>
+        <v>-0.1618</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1624</v>
+        <v>-0.1618</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1624</v>
+        <v>-0.1618</v>
       </c>
       <c r="I52" t="n">
         <v>-0.1632</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0723</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4906</v>
+        <v>-0.5122</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1713</v>
@@ -2894,7 +2894,7 @@
         <v>-0.09569999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5129</v>
+        <v>-0.5342</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2267</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2915</v>
+        <v>-0.2872</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.123</v>
+        <v>-0.1212</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5391</v>
+        <v>-0.5583</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2915</v>
+        <v>-0.2872</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2915</v>
+        <v>-0.2872</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2915</v>
+        <v>-0.2872</v>
       </c>
       <c r="I55" t="n">
         <v>-0.297</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3006</v>
+        <v>-0.2995</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1268</v>
+        <v>-0.1264</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5632</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3006</v>
+        <v>-0.2995</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3006</v>
+        <v>-0.2995</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3006</v>
+        <v>-0.2995</v>
       </c>
       <c r="I56" t="n">
         <v>-0.302</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3015</v>
+        <v>-0.3004</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1272</v>
+        <v>-0.1268</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5432</v>
+        <v>-0.5636</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3015</v>
+        <v>-0.3004</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3015</v>
+        <v>-0.3004</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3015</v>
+        <v>-0.3004</v>
       </c>
       <c r="I57" t="n">
         <v>-0.3029</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3578</v>
+        <v>-0.3512</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.151</v>
+        <v>-0.1482</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5659</v>
+        <v>-0.5838</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3578</v>
+        <v>-0.3512</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3578</v>
+        <v>-0.3512</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3578</v>
+        <v>-0.3512</v>
       </c>
       <c r="I58" t="n">
         <v>-0.3662</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3965</v>
+        <v>-0.395</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1673</v>
+        <v>-0.1667</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5815</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3965</v>
+        <v>-0.395</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3965</v>
+        <v>-0.395</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3965</v>
+        <v>-0.395</v>
       </c>
       <c r="I59" t="n">
         <v>-0.3983</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.424</v>
+        <v>-0.4177</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1789</v>
+        <v>-0.1763</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5926</v>
+        <v>-0.6103</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.424</v>
+        <v>-0.4177</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.424</v>
+        <v>-0.4177</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.424</v>
+        <v>-0.4177</v>
       </c>
       <c r="I60" t="n">
         <v>-0.4319</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4597</v>
+        <v>-0.4579</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.194</v>
+        <v>-0.1932</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6071</v>
+        <v>-0.6263</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4597</v>
+        <v>-0.4579</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.4597</v>
+        <v>-0.4579</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.4597</v>
+        <v>-0.4579</v>
       </c>
       <c r="I61" t="n">
         <v>-0.4618</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5798</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2447</v>
+        <v>-0.2392</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6556</v>
+        <v>-0.6698</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5798</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5798</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5798</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="I62" t="n">
         <v>-0.5962</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6637</v>
+        <v>-0.6612</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2801</v>
+        <v>-0.279</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6895</v>
+        <v>-0.7073</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6637</v>
+        <v>-0.6612</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6637</v>
+        <v>-0.6612</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6637</v>
+        <v>-0.6612</v>
       </c>
       <c r="I63" t="n">
         <v>-0.6667999999999999</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3771</v>
+        <v>-0.3728</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7824</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="I64" t="n">
         <v>-0.9061</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.0029</v>
+        <v>-0.9992</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4232</v>
+        <v>-0.4216</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8265</v>
+        <v>-0.842</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.0029</v>
+        <v>-0.9992</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.0029</v>
+        <v>-0.9992</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.0029</v>
+        <v>-0.9992</v>
       </c>
       <c r="I65" t="n">
         <v>-1.0076</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0431</v>
+        <v>-1.0238</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4401</v>
+        <v>-0.432</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8428</v>
+        <v>-0.8518</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.0431</v>
+        <v>-1.0238</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.0431</v>
+        <v>-1.0238</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.0431</v>
+        <v>-1.0238</v>
       </c>
       <c r="I66" t="n">
         <v>-1.0676</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1174</v>
+        <v>-1.105</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4715</v>
+        <v>-0.4663</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8728</v>
+        <v>-0.8841</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.1174</v>
+        <v>-1.105</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.1174</v>
+        <v>-1.105</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.1174</v>
+        <v>-1.105</v>
       </c>
       <c r="I67" t="n">
         <v>-1.1331</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1287</v>
+        <v>-1.1203</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4763</v>
+        <v>-0.4727</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8773</v>
+        <v>-0.8902</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.1287</v>
+        <v>-1.1203</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.1287</v>
+        <v>-1.1203</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.1287</v>
+        <v>-1.1203</v>
       </c>
       <c r="I68" t="n">
         <v>-1.1392</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1288</v>
+        <v>-1.1246</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4763</v>
+        <v>-0.4745</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8774</v>
+        <v>-0.892</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1288</v>
+        <v>-1.1246</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1288</v>
+        <v>-1.1246</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1288</v>
+        <v>-1.1246</v>
       </c>
       <c r="I69" t="n">
         <v>-1.1341</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1388</v>
+        <v>-1.1346</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4805</v>
+        <v>-0.4788</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8814</v>
+        <v>-0.8959</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1388</v>
+        <v>-1.1346</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.1388</v>
+        <v>-1.1346</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.1388</v>
+        <v>-1.1346</v>
       </c>
       <c r="I70" t="n">
         <v>-1.1441</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.1775</v>
+        <v>-1.1731</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4969</v>
+        <v>-0.495</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.897</v>
+        <v>-0.9113</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.1775</v>
+        <v>-1.1731</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.1775</v>
+        <v>-1.1731</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.1775</v>
+        <v>-1.1731</v>
       </c>
       <c r="I71" t="n">
         <v>-1.183</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3032</v>
+        <v>-1.2743</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.5377</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9478</v>
+        <v>-0.9516</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3032</v>
+        <v>-1.2743</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.3032</v>
+        <v>-1.2743</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.3032</v>
+        <v>-1.2743</v>
       </c>
       <c r="I72" t="n">
         <v>-1.34</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.328</v>
+        <v>-1.3034</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5604</v>
+        <v>-0.55</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9578</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.328</v>
+        <v>-1.3034</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.328</v>
+        <v>-1.3034</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.328</v>
+        <v>-1.3034</v>
       </c>
       <c r="I73" t="n">
         <v>-1.3592</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.3647</v>
+        <v>-1.3494</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5758</v>
+        <v>-0.5694</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9727</v>
+        <v>-0.9815</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.3647</v>
+        <v>-1.3494</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.3647</v>
+        <v>-1.3494</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.3647</v>
+        <v>-1.3494</v>
       </c>
       <c r="I74" t="n">
         <v>-1.3838</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.5138</v>
+        <v>-1.5025</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6388</v>
+        <v>-0.634</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0329</v>
+        <v>-1.0425</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.5138</v>
+        <v>-1.5025</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.5138</v>
+        <v>-1.5025</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.5138</v>
+        <v>-1.5025</v>
       </c>
       <c r="I75" t="n">
         <v>-1.5279</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.7774</v>
+        <v>-1.7708</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.75</v>
+        <v>-0.7472</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1394</v>
+        <v>-1.1494</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.7774</v>
+        <v>-1.7708</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.7774</v>
+        <v>-1.7708</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.7774</v>
+        <v>-1.7708</v>
       </c>
       <c r="I76" t="n">
         <v>-1.7857</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>imoRR</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.9907</v>
+        <v>-1.9532</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.84</v>
+        <v>-0.8242</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2256</v>
+        <v>-1.2221</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.9907</v>
+        <v>-1.9532</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.9907</v>
+        <v>-1.9532</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.9907</v>
+        <v>-1.9532</v>
       </c>
       <c r="I77" t="n">
-        <v>-2</v>
+        <v>-2.0539</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>131</v>
+        <v>348</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2</v>
+        <v>-2.0539</v>
       </c>
       <c r="N77" t="n">
-        <v>131</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>imoRR</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.9975</v>
+        <v>-1.9833</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8429</v>
+        <v>-0.8369</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2283</v>
+        <v>-1.2341</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.9975</v>
+        <v>-1.9833</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.9975</v>
+        <v>-1.9833</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.9975</v>
+        <v>-1.9833</v>
       </c>
       <c r="I78" t="n">
-        <v>-2.0539</v>
+        <v>-2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>348</v>
+        <v>131</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.0539</v>
+        <v>-2</v>
       </c>
       <c r="N78" t="n">
-        <v>348</v>
+        <v>131</v>
       </c>
     </row>
     <row r="79">
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.1418</v>
+        <v>-2.0632</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.8706</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2866</v>
+        <v>-1.2659</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.1418</v>
+        <v>-2.0632</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.1418</v>
+        <v>-2.0632</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.1418</v>
+        <v>-2.0632</v>
       </c>
       <c r="I79" t="n">
         <v>-2.2436</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.1629</v>
+        <v>-2.1309</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.9127</v>
+        <v>-0.8991</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2951</v>
+        <v>-1.2929</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.1629</v>
+        <v>-2.1309</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.1629</v>
+        <v>-2.1309</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.1629</v>
+        <v>-2.1309</v>
       </c>
       <c r="I80" t="n">
         <v>-2.2035</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.3351</v>
+        <v>-2.3005</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.9853</v>
+        <v>-0.9707</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.3647</v>
+        <v>-1.3604</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.3351</v>
+        <v>-2.3005</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.3351</v>
+        <v>-2.3005</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.3351</v>
+        <v>-2.3005</v>
       </c>
       <c r="I81" t="n">
         <v>-2.3789</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.4869</v>
+        <v>-2.4684</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.0494</v>
+        <v>-1.0416</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.426</v>
+        <v>-1.4273</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.4869</v>
+        <v>-2.4684</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.4869</v>
+        <v>-2.4684</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.4869</v>
+        <v>-2.4684</v>
       </c>
       <c r="I82" t="n">
         <v>-2.5101</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-3.9016</v>
+        <v>-3.815</v>
       </c>
       <c r="C83" t="n">
-        <v>-1.6463</v>
+        <v>-1.6098</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.9975</v>
+        <v>-1.9638</v>
       </c>
       <c r="E83" t="n">
-        <v>-3.9016</v>
+        <v>-3.815</v>
       </c>
       <c r="F83" t="n">
-        <v>-3.9016</v>
+        <v>-3.815</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-3.9016</v>
+        <v>-3.815</v>
       </c>
       <c r="I83" t="n">
         <v>-4.0118</v>
